--- a/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487873_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487873_PROCESSED_CHRONO.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>M. OLAIZOLA GARIN</t>
+          <t>I. AIZPITARTE ARANZA</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>3.0448</v>
+        <v>4.0545</v>
       </c>
       <c r="E2" t="n">
-        <v>1.4951</v>
+        <v>3.6484</v>
       </c>
       <c r="F2" t="n">
-        <v>1.5497</v>
+        <v>0.4061</v>
       </c>
       <c r="G2" t="n">
-        <v>1.8051</v>
+        <v>0.6513</v>
       </c>
       <c r="H2" t="n">
-        <v>0.7102000000000001</v>
+        <v>-1.8429</v>
       </c>
       <c r="I2" t="n">
-        <v>1.0948</v>
+        <v>2.4942</v>
       </c>
       <c r="J2" t="n">
-        <v>0.9112</v>
+        <v>1.4843</v>
       </c>
       <c r="K2" t="n">
-        <v>0.9594</v>
+        <v>-0.6833</v>
       </c>
       <c r="L2" t="n">
-        <v>-0.0482</v>
+        <v>2.1676</v>
       </c>
       <c r="M2" t="n">
-        <v>0.8938</v>
+        <v>-0.833</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.2492</v>
+        <v>-1.1596</v>
       </c>
       <c r="O2" t="n">
-        <v>1.143</v>
+        <v>0.3266</v>
       </c>
       <c r="P2" t="n">
-        <v>1.0406</v>
+        <v>0.8325</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>-1.0406</v>
       </c>
       <c r="R2" t="n">
-        <v>1.0406</v>
+        <v>1.8731</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.1546</v>
+        <v>0.5895</v>
       </c>
       <c r="T2" t="n">
-        <v>0.5839</v>
+        <v>0.6395999999999999</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.7385</v>
+        <v>-0.0502</v>
       </c>
       <c r="V2" t="n">
-        <v>0.3538</v>
+        <v>1.9813</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>2.565</v>
       </c>
       <c r="X2" t="n">
-        <v>0.3538</v>
+        <v>-0.5838</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>I. AIZPITARTE ARANZA</t>
+          <t>M. OLAIZOLA GARIN</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,67 +643,67 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.7578</v>
+        <v>2.948</v>
       </c>
       <c r="E3" t="n">
-        <v>2.3811</v>
+        <v>1.2808</v>
       </c>
       <c r="F3" t="n">
-        <v>0.3768</v>
+        <v>1.6672</v>
       </c>
       <c r="G3" t="n">
-        <v>0.6513</v>
+        <v>1.8051</v>
       </c>
       <c r="H3" t="n">
-        <v>-1.8429</v>
+        <v>0.7102000000000001</v>
       </c>
       <c r="I3" t="n">
-        <v>2.4942</v>
+        <v>1.0948</v>
       </c>
       <c r="J3" t="n">
-        <v>1.4843</v>
+        <v>0.9112</v>
       </c>
       <c r="K3" t="n">
-        <v>-0.6833</v>
+        <v>0.9594</v>
       </c>
       <c r="L3" t="n">
-        <v>2.1676</v>
+        <v>-0.0482</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.833</v>
+        <v>0.8938</v>
       </c>
       <c r="N3" t="n">
-        <v>-1.1596</v>
+        <v>-0.2492</v>
       </c>
       <c r="O3" t="n">
-        <v>0.3266</v>
+        <v>1.143</v>
       </c>
       <c r="P3" t="n">
-        <v>0.8325</v>
+        <v>1.0406</v>
       </c>
       <c r="Q3" t="n">
-        <v>-1.0406</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>1.8731</v>
+        <v>1.0406</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.7072000000000001</v>
+        <v>-0.2515</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.6277</v>
+        <v>0.3696</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.0795</v>
+        <v>-0.6211</v>
       </c>
       <c r="V3" t="n">
-        <v>1.9813</v>
+        <v>0.3538</v>
       </c>
       <c r="W3" t="n">
-        <v>2.565</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.5838</v>
+        <v>0.3538</v>
       </c>
     </row>
     <row r="4">
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.3246</v>
+        <v>2.476</v>
       </c>
       <c r="E4" t="n">
-        <v>1.2889</v>
+        <v>2.2347</v>
       </c>
       <c r="F4" t="n">
-        <v>0.0357</v>
+        <v>0.2413</v>
       </c>
       <c r="G4" t="n">
         <v>0.8585</v>
@@ -766,13 +766,13 @@
         <v>2.4974</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.7607</v>
+        <v>0.3906</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.0438</v>
+        <v>0.9021</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.7169</v>
+        <v>-0.5114</v>
       </c>
       <c r="V4" t="n">
         <v>-0.23</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.8875999999999999</v>
+        <v>1.2972</v>
       </c>
       <c r="E5" t="n">
-        <v>1.1407</v>
+        <v>1.4621</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.253</v>
+        <v>-0.1649</v>
       </c>
       <c r="G5" t="n">
         <v>-0.2515</v>
@@ -844,13 +844,13 @@
         <v>0.2081</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.0065</v>
+        <v>0.403</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.06519999999999999</v>
+        <v>0.2562</v>
       </c>
       <c r="U5" t="n">
-        <v>0.0587</v>
+        <v>0.1468</v>
       </c>
       <c r="V5" t="n">
         <v>0.9376</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>P. BADJI</t>
+          <t>M. NIANG NDONGO</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.4328</v>
+        <v>0.5675</v>
       </c>
       <c r="E6" t="n">
-        <v>1.5789</v>
+        <v>1.9643</v>
       </c>
       <c r="F6" t="n">
-        <v>-1.1461</v>
+        <v>-1.3968</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.6872</v>
+        <v>-2.148</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.5762</v>
+        <v>-0.9724</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.111</v>
+        <v>-1.1756</v>
       </c>
       <c r="J6" t="n">
-        <v>1.7623</v>
+        <v>0.9588</v>
       </c>
       <c r="K6" t="n">
-        <v>1.0569</v>
+        <v>1.1425</v>
       </c>
       <c r="L6" t="n">
-        <v>0.7054</v>
+        <v>-0.1837</v>
       </c>
       <c r="M6" t="n">
-        <v>-2.4495</v>
+        <v>-3.1068</v>
       </c>
       <c r="N6" t="n">
-        <v>-1.6331</v>
+        <v>-2.1148</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.8164</v>
+        <v>-0.9919</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.4162</v>
+        <v>-0.2081</v>
       </c>
       <c r="Q6" t="n">
         <v>-2.0812</v>
       </c>
       <c r="R6" t="n">
-        <v>1.6649</v>
+        <v>1.8731</v>
       </c>
       <c r="S6" t="n">
-        <v>1.89</v>
+        <v>1.4023</v>
       </c>
       <c r="T6" t="n">
-        <v>1.4378</v>
+        <v>1.1054</v>
       </c>
       <c r="U6" t="n">
-        <v>0.4522</v>
+        <v>0.2969</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.3538</v>
+        <v>1.5213</v>
       </c>
       <c r="W6" t="n">
-        <v>0.4599</v>
+        <v>1.9813</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.8137</v>
+        <v>-0.4599</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>M. NIANG NDONGO</t>
+          <t>O. ARDANZA BERNAOLA</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.4099</v>
+        <v>-0.2984</v>
       </c>
       <c r="E7" t="n">
-        <v>1.9828</v>
+        <v>0.1319</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.5729</v>
+        <v>-0.4303</v>
       </c>
       <c r="G7" t="n">
-        <v>-2.148</v>
+        <v>-2.3568</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.9724</v>
+        <v>-2.6908</v>
       </c>
       <c r="I7" t="n">
-        <v>-1.1756</v>
+        <v>0.3339</v>
       </c>
       <c r="J7" t="n">
-        <v>0.9588</v>
+        <v>-0.7156</v>
       </c>
       <c r="K7" t="n">
-        <v>1.1425</v>
+        <v>-1.2944</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.1837</v>
+        <v>0.5788</v>
       </c>
       <c r="M7" t="n">
-        <v>-3.1068</v>
+        <v>-1.6412</v>
       </c>
       <c r="N7" t="n">
-        <v>-2.1148</v>
+        <v>-1.3963</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.9919</v>
+        <v>-0.2449</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.2081</v>
+        <v>0.2081</v>
       </c>
       <c r="Q7" t="n">
-        <v>-2.0812</v>
+        <v>-1.0406</v>
       </c>
       <c r="R7" t="n">
-        <v>1.8731</v>
+        <v>1.2487</v>
       </c>
       <c r="S7" t="n">
-        <v>1.2447</v>
+        <v>0.4528</v>
       </c>
       <c r="T7" t="n">
-        <v>1.124</v>
+        <v>0.4906</v>
       </c>
       <c r="U7" t="n">
-        <v>0.1207</v>
+        <v>-0.0378</v>
       </c>
       <c r="V7" t="n">
-        <v>1.5213</v>
+        <v>1.3975</v>
       </c>
       <c r="W7" t="n">
-        <v>1.9813</v>
+        <v>1.3975</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.4599</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>O. ARDANZA BERNAOLA</t>
+          <t>P. BADJI</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.5868</v>
+        <v>-0.548</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.362</v>
+        <v>0.7449</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.2248</v>
+        <v>-1.2929</v>
       </c>
       <c r="G8" t="n">
-        <v>-2.3568</v>
+        <v>-0.6872</v>
       </c>
       <c r="H8" t="n">
-        <v>-2.6908</v>
+        <v>-0.5762</v>
       </c>
       <c r="I8" t="n">
-        <v>0.3339</v>
+        <v>-0.111</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.7156</v>
+        <v>1.7623</v>
       </c>
       <c r="K8" t="n">
-        <v>-1.2944</v>
+        <v>1.0569</v>
       </c>
       <c r="L8" t="n">
-        <v>0.5788</v>
+        <v>0.7054</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.6412</v>
+        <v>-2.4495</v>
       </c>
       <c r="N8" t="n">
-        <v>-1.3963</v>
+        <v>-1.6331</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.2449</v>
+        <v>-0.8164</v>
       </c>
       <c r="P8" t="n">
-        <v>0.2081</v>
+        <v>-0.4162</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.0406</v>
+        <v>-2.0812</v>
       </c>
       <c r="R8" t="n">
-        <v>1.2487</v>
+        <v>1.6649</v>
       </c>
       <c r="S8" t="n">
-        <v>0.1644</v>
+        <v>0.9093</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.0033</v>
+        <v>0.6039</v>
       </c>
       <c r="U8" t="n">
-        <v>0.1677</v>
+        <v>0.3054</v>
       </c>
       <c r="V8" t="n">
-        <v>1.3975</v>
+        <v>-0.3538</v>
       </c>
       <c r="W8" t="n">
-        <v>1.3975</v>
+        <v>0.4599</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>-0.8137</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>J. CEBOLLA HERRERA</t>
+          <t>N. WILLIAMS</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.9347</v>
+        <v>-0.5487</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.4788</v>
+        <v>-1.1725</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.4558</v>
+        <v>0.6238</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.0181</v>
+        <v>-0.1114</v>
       </c>
       <c r="H9" t="n">
-        <v>-1.29</v>
+        <v>0.6332</v>
       </c>
       <c r="I9" t="n">
-        <v>0.2719</v>
+        <v>-0.7446</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.08740000000000001</v>
+        <v>0.3949</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.7144</v>
+        <v>1.0701</v>
       </c>
       <c r="L9" t="n">
-        <v>0.627</v>
+        <v>-0.6752</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.9308</v>
+        <v>-0.5063</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.5756</v>
+        <v>-0.4369</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.3551</v>
+        <v>-0.0694</v>
       </c>
       <c r="P9" t="n">
-        <v>0.4162</v>
+        <v>-1.6649</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>-2.0812</v>
       </c>
       <c r="R9" t="n">
         <v>0.4162</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.3327</v>
+        <v>0.1662</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.3915</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="U9" t="n">
-        <v>0.0587</v>
+        <v>0.2362</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>1.0614</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>0.5838</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>0.4776</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>N. WILLIAMS</t>
+          <t>J. CEBOLLA HERRERA</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.9876</v>
+        <v>-0.7393999999999999</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.4939</v>
+        <v>-0.3717</v>
       </c>
       <c r="F10" t="n">
-        <v>0.5063</v>
+        <v>-0.3678</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.1114</v>
+        <v>-1.0181</v>
       </c>
       <c r="H10" t="n">
-        <v>0.6332</v>
+        <v>-1.29</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.7446</v>
+        <v>0.2719</v>
       </c>
       <c r="J10" t="n">
-        <v>0.3949</v>
+        <v>-0.08740000000000001</v>
       </c>
       <c r="K10" t="n">
-        <v>1.0701</v>
+        <v>-0.7144</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.6752</v>
+        <v>0.627</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.5063</v>
+        <v>-0.9308</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.4369</v>
+        <v>-0.5756</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.0694</v>
+        <v>-0.3551</v>
       </c>
       <c r="P10" t="n">
-        <v>-1.6649</v>
+        <v>0.4162</v>
       </c>
       <c r="Q10" t="n">
-        <v>-2.0812</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
         <v>0.4162</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.2727</v>
+        <v>-0.1375</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.3915</v>
+        <v>-0.2843</v>
       </c>
       <c r="U10" t="n">
-        <v>0.1188</v>
+        <v>0.1468</v>
       </c>
       <c r="V10" t="n">
-        <v>1.0614</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>0.5838</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>0.4776</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>T. SAGNA</t>
+          <t>A. ACHA CORTABARRIA</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1267,73 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.0376</v>
+        <v>-0.8279</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.0594</v>
+        <v>-1.1889</v>
       </c>
       <c r="F11" t="n">
-        <v>1.0218</v>
+        <v>0.361</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.8802</v>
+        <v>-1.1685</v>
       </c>
       <c r="H11" t="n">
-        <v>-1.8615</v>
+        <v>-0.6542</v>
       </c>
       <c r="I11" t="n">
-        <v>0.9814000000000001</v>
+        <v>-0.5143</v>
       </c>
       <c r="J11" t="n">
-        <v>-1.3576</v>
+        <v>-0.9641999999999999</v>
       </c>
       <c r="K11" t="n">
-        <v>-1.5143</v>
+        <v>0.2686</v>
       </c>
       <c r="L11" t="n">
-        <v>0.1568</v>
+        <v>-1.2328</v>
       </c>
       <c r="M11" t="n">
-        <v>0.4774</v>
+        <v>-0.2044</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.3472</v>
+        <v>-0.9228</v>
       </c>
       <c r="O11" t="n">
-        <v>0.8246</v>
+        <v>0.7185</v>
       </c>
       <c r="P11" t="n">
-        <v>-1.8731</v>
+        <v>-1.0406</v>
       </c>
       <c r="Q11" t="n">
         <v>-3.1218</v>
       </c>
       <c r="R11" t="n">
-        <v>1.2487</v>
+        <v>2.0812</v>
       </c>
       <c r="S11" t="n">
-        <v>3.4669</v>
+        <v>0.2137</v>
       </c>
       <c r="T11" t="n">
-        <v>3.1276</v>
+        <v>0.5620000000000001</v>
       </c>
       <c r="U11" t="n">
-        <v>0.3393</v>
+        <v>-0.3483</v>
       </c>
       <c r="V11" t="n">
-        <v>-1.7513</v>
+        <v>1.1675</v>
       </c>
       <c r="W11" t="n">
-        <v>-0.7076</v>
+        <v>2.3351</v>
       </c>
       <c r="X11" t="n">
-        <v>-1.0437</v>
+        <v>-1.1675</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A. ACHA CORTABARRIA</t>
+          <t>T. SAGNA</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-1.0846</v>
+        <v>-3.1757</v>
       </c>
       <c r="E12" t="n">
-        <v>-1.5337</v>
+        <v>-3.8158</v>
       </c>
       <c r="F12" t="n">
-        <v>0.449</v>
+        <v>0.6401</v>
       </c>
       <c r="G12" t="n">
-        <v>-1.1685</v>
+        <v>-0.8802</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.6542</v>
+        <v>-1.8615</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.5143</v>
+        <v>0.9814000000000001</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.9641999999999999</v>
+        <v>-1.3576</v>
       </c>
       <c r="K12" t="n">
-        <v>0.2686</v>
+        <v>-1.5143</v>
       </c>
       <c r="L12" t="n">
-        <v>-1.2328</v>
+        <v>0.1568</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.2044</v>
+        <v>0.4774</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.9228</v>
+        <v>-0.3472</v>
       </c>
       <c r="O12" t="n">
-        <v>0.7185</v>
+        <v>0.8246</v>
       </c>
       <c r="P12" t="n">
-        <v>-1.0406</v>
+        <v>-1.8731</v>
       </c>
       <c r="Q12" t="n">
         <v>-3.1218</v>
       </c>
       <c r="R12" t="n">
-        <v>2.0812</v>
+        <v>1.2487</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.043</v>
+        <v>1.3288</v>
       </c>
       <c r="T12" t="n">
-        <v>0.2172</v>
+        <v>1.3711</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.2602</v>
+        <v>-0.0423</v>
       </c>
       <c r="V12" t="n">
-        <v>1.1675</v>
+        <v>-1.7513</v>
       </c>
       <c r="W12" t="n">
-        <v>2.3351</v>
+        <v>-0.7076</v>
       </c>
       <c r="X12" t="n">
-        <v>-1.1675</v>
+        <v>-1.0437</v>
       </c>
     </row>
     <row r="13">
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>4.226200000000001</v>
+        <v>5.205100000000001</v>
       </c>
       <c r="E13" t="n">
-        <v>3.9397</v>
+        <v>4.918199999999999</v>
       </c>
       <c r="F13" t="n">
-        <v>0.2867000000000001</v>
+        <v>0.2868000000000002</v>
       </c>
       <c r="G13" t="n">
         <v>-5.306800000000001</v>
@@ -1447,7 +1447,7 @@
         <v>1.0838</v>
       </c>
       <c r="L13" t="n">
-        <v>3.714599999999999</v>
+        <v>3.7146</v>
       </c>
       <c r="M13" t="n">
         <v>-10.1055</v>
@@ -1456,7 +1456,7 @@
         <v>-10.8606</v>
       </c>
       <c r="O13" t="n">
-        <v>0.7554999999999998</v>
+        <v>0.7554999999999997</v>
       </c>
       <c r="P13" t="n">
         <v>-1.0406</v>
@@ -1468,19 +1468,19 @@
         <v>14.5682</v>
       </c>
       <c r="S13" t="n">
-        <v>4.488599999999999</v>
+        <v>5.467200000000001</v>
       </c>
       <c r="T13" t="n">
-        <v>4.9675</v>
+        <v>5.9462</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.479</v>
+        <v>-0.4789999999999999</v>
       </c>
       <c r="V13" t="n">
         <v>6.0853</v>
       </c>
       <c r="W13" t="n">
-        <v>9.782499999999999</v>
+        <v>9.782500000000001</v>
       </c>
       <c r="X13" t="n">
         <v>-3.6972</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>5.207</v>
+        <v>4.4721</v>
       </c>
       <c r="E14" t="n">
-        <v>5.9952</v>
+        <v>5.3522</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.7881</v>
+        <v>-0.8801</v>
       </c>
       <c r="G14" t="n">
         <v>4.94</v>
@@ -1546,13 +1546,13 @@
         <v>2.0812</v>
       </c>
       <c r="S14" t="n">
-        <v>0.8716</v>
+        <v>0.1367</v>
       </c>
       <c r="T14" t="n">
-        <v>0.8383</v>
+        <v>0.1953</v>
       </c>
       <c r="U14" t="n">
-        <v>0.0334</v>
+        <v>-0.0586</v>
       </c>
       <c r="V14" t="n">
         <v>-1.6452</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>3.0843</v>
+        <v>3.0637</v>
       </c>
       <c r="E15" t="n">
-        <v>1.2331</v>
+        <v>1.4474</v>
       </c>
       <c r="F15" t="n">
-        <v>1.8513</v>
+        <v>1.6164</v>
       </c>
       <c r="G15" t="n">
         <v>2.0766</v>
@@ -1624,13 +1624,13 @@
         <v>2.0812</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.7405</v>
+        <v>-0.761</v>
       </c>
       <c r="T15" t="n">
-        <v>0.0091</v>
+        <v>0.2234</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.7496</v>
+        <v>-0.9844000000000001</v>
       </c>
       <c r="V15" t="n">
         <v>0.7076</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.6172</v>
+        <v>2.7894</v>
       </c>
       <c r="E16" t="n">
         <v>3.1431</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.526</v>
+        <v>-0.3537</v>
       </c>
       <c r="G16" t="n">
         <v>3.5419</v>
@@ -1702,13 +1702,13 @@
         <v>0.8325</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.4867</v>
+        <v>-0.3144</v>
       </c>
       <c r="T16" t="n">
         <v>-0.5096000000000001</v>
       </c>
       <c r="U16" t="n">
-        <v>0.0229</v>
+        <v>0.1951</v>
       </c>
       <c r="V16" t="n">
         <v>-0.23</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>H. ARBOSA ROLDAN</t>
+          <t>V. HRABAR</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.7679</v>
+        <v>2.6576</v>
       </c>
       <c r="E17" t="n">
-        <v>1.4306</v>
+        <v>2.8882</v>
       </c>
       <c r="F17" t="n">
-        <v>0.3373</v>
+        <v>-0.2306</v>
       </c>
       <c r="G17" t="n">
-        <v>1.057</v>
+        <v>3.3007</v>
       </c>
       <c r="H17" t="n">
-        <v>1.177</v>
+        <v>2.3096</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.12</v>
+        <v>0.9911</v>
       </c>
       <c r="J17" t="n">
-        <v>2.3879</v>
+        <v>3.2316</v>
       </c>
       <c r="K17" t="n">
-        <v>1.7609</v>
+        <v>1.9956</v>
       </c>
       <c r="L17" t="n">
-        <v>0.627</v>
+        <v>1.236</v>
       </c>
       <c r="M17" t="n">
-        <v>-1.331</v>
+        <v>0.06909999999999999</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.5839</v>
+        <v>0.314</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.747</v>
+        <v>-0.2449</v>
       </c>
       <c r="P17" t="n">
-        <v>-1.6649</v>
+        <v>1.6649</v>
       </c>
       <c r="Q17" t="n">
-        <v>-3.1218</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>1.4568</v>
+        <v>1.6649</v>
       </c>
       <c r="S17" t="n">
-        <v>1.7921</v>
+        <v>-1.3705</v>
       </c>
       <c r="T17" t="n">
-        <v>1.5807</v>
+        <v>-0.5734</v>
       </c>
       <c r="U17" t="n">
-        <v>0.2114</v>
+        <v>-0.7972</v>
       </c>
       <c r="V17" t="n">
-        <v>0.5838</v>
+        <v>-0.9376</v>
       </c>
       <c r="W17" t="n">
-        <v>0.5838</v>
+        <v>0.23</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>-1.1675</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>V. HRABAR</t>
+          <t>H. ARBOSA ROLDAN</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,67 +1813,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>1.5131</v>
+        <v>0.5099</v>
       </c>
       <c r="E18" t="n">
-        <v>2.3525</v>
+        <v>0.4662</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.8393</v>
+        <v>0.0437</v>
       </c>
       <c r="G18" t="n">
-        <v>3.3007</v>
+        <v>1.057</v>
       </c>
       <c r="H18" t="n">
-        <v>2.3096</v>
+        <v>1.177</v>
       </c>
       <c r="I18" t="n">
-        <v>0.9911</v>
+        <v>-0.12</v>
       </c>
       <c r="J18" t="n">
-        <v>3.2316</v>
+        <v>2.3879</v>
       </c>
       <c r="K18" t="n">
-        <v>1.9956</v>
+        <v>1.7609</v>
       </c>
       <c r="L18" t="n">
-        <v>1.236</v>
+        <v>0.627</v>
       </c>
       <c r="M18" t="n">
-        <v>0.06909999999999999</v>
+        <v>-1.331</v>
       </c>
       <c r="N18" t="n">
-        <v>0.314</v>
+        <v>-0.5839</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.2449</v>
+        <v>-0.747</v>
       </c>
       <c r="P18" t="n">
-        <v>1.6649</v>
+        <v>-1.6649</v>
       </c>
       <c r="Q18" t="n">
+        <v>-3.1218</v>
+      </c>
+      <c r="R18" t="n">
+        <v>1.4568</v>
+      </c>
+      <c r="S18" t="n">
+        <v>0.5341</v>
+      </c>
+      <c r="T18" t="n">
+        <v>0.6163</v>
+      </c>
+      <c r="U18" t="n">
+        <v>-0.0822</v>
+      </c>
+      <c r="V18" t="n">
+        <v>0.5838</v>
+      </c>
+      <c r="W18" t="n">
+        <v>0.5838</v>
+      </c>
+      <c r="X18" t="n">
         <v>0</v>
-      </c>
-      <c r="R18" t="n">
-        <v>1.6649</v>
-      </c>
-      <c r="S18" t="n">
-        <v>-2.515</v>
-      </c>
-      <c r="T18" t="n">
-        <v>-1.1091</v>
-      </c>
-      <c r="U18" t="n">
-        <v>-1.4059</v>
-      </c>
-      <c r="V18" t="n">
-        <v>-0.9376</v>
-      </c>
-      <c r="W18" t="n">
-        <v>0.23</v>
-      </c>
-      <c r="X18" t="n">
-        <v>-1.1675</v>
       </c>
     </row>
     <row r="19">
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.0481</v>
+        <v>-0.4893</v>
       </c>
       <c r="E19" t="n">
-        <v>0.0423</v>
+        <v>0.2567</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.0905</v>
+        <v>-0.746</v>
       </c>
       <c r="G19" t="n">
         <v>0.9434</v>
@@ -1936,13 +1936,13 @@
         <v>1.2487</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.6752</v>
+        <v>-0.1164</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.7053</v>
+        <v>-0.491</v>
       </c>
       <c r="U19" t="n">
-        <v>0.0301</v>
+        <v>0.3745</v>
       </c>
       <c r="V19" t="n">
         <v>-2.565</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.0035</v>
+        <v>-2.417</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.5422</v>
+        <v>-1.8636</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.4614</v>
+        <v>-0.5534</v>
       </c>
       <c r="G20" t="n">
         <v>-0.9802</v>
@@ -2014,13 +2014,13 @@
         <v>1.0406</v>
       </c>
       <c r="S20" t="n">
-        <v>0.2473</v>
+        <v>-0.1662</v>
       </c>
       <c r="T20" t="n">
-        <v>0.5434</v>
+        <v>0.222</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.2962</v>
+        <v>-0.3882</v>
       </c>
       <c r="V20" t="n">
         <v>-0.23</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>J. PARDINA MOLINA</t>
+          <t>K. TORRES CUEVAS</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-3.669</v>
+        <v>-2.6245</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.2027</v>
+        <v>-2.9643</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.4663</v>
+        <v>0.3398</v>
       </c>
       <c r="G21" t="n">
-        <v>-1.2186</v>
+        <v>-3.2853</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.1213</v>
+        <v>-1.3242</v>
       </c>
       <c r="I21" t="n">
-        <v>-1.0973</v>
+        <v>-1.9611</v>
       </c>
       <c r="J21" t="n">
-        <v>-1.1777</v>
+        <v>-2.1666</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.5417</v>
+        <v>-0.5933</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.636</v>
+        <v>-1.5733</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.0409</v>
+        <v>-1.1187</v>
       </c>
       <c r="N21" t="n">
-        <v>0.4203</v>
+        <v>-0.731</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.4613</v>
+        <v>-0.3878</v>
       </c>
       <c r="P21" t="n">
-        <v>-0.2081</v>
+        <v>1.4568</v>
       </c>
       <c r="Q21" t="n">
         <v>-1.0406</v>
       </c>
       <c r="R21" t="n">
-        <v>0.8325</v>
+        <v>2.4974</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.7209</v>
+        <v>-0.5484</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.4443</v>
+        <v>0.2606</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.2766</v>
+        <v>-0.8089</v>
       </c>
       <c r="V21" t="n">
-        <v>-1.5213</v>
+        <v>-0.2477</v>
       </c>
       <c r="W21" t="n">
-        <v>0.4599</v>
+        <v>-0.0177</v>
       </c>
       <c r="X21" t="n">
-        <v>-1.9813</v>
+        <v>-0.23</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>K. TORRES CUEVAS</t>
+          <t>J. PARDINA MOLINA</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.7039</v>
+        <v>-2.8665</v>
       </c>
       <c r="E22" t="n">
-        <v>-3.6072</v>
+        <v>-1.774</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.09669999999999999</v>
+        <v>-1.0925</v>
       </c>
       <c r="G22" t="n">
-        <v>-3.2853</v>
+        <v>-1.2186</v>
       </c>
       <c r="H22" t="n">
-        <v>-1.3242</v>
+        <v>-0.1213</v>
       </c>
       <c r="I22" t="n">
-        <v>-1.9611</v>
+        <v>-1.0973</v>
       </c>
       <c r="J22" t="n">
-        <v>-2.1666</v>
+        <v>-1.1777</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.5933</v>
+        <v>-0.5417</v>
       </c>
       <c r="L22" t="n">
-        <v>-1.5733</v>
+        <v>-0.636</v>
       </c>
       <c r="M22" t="n">
-        <v>-1.1187</v>
+        <v>-0.0409</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.731</v>
+        <v>0.4203</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.3878</v>
+        <v>-0.4613</v>
       </c>
       <c r="P22" t="n">
-        <v>1.4568</v>
+        <v>-0.2081</v>
       </c>
       <c r="Q22" t="n">
         <v>-1.0406</v>
       </c>
       <c r="R22" t="n">
-        <v>2.4974</v>
+        <v>0.8325</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.6278</v>
+        <v>0.08160000000000001</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.3824</v>
+        <v>-0.0157</v>
       </c>
       <c r="U22" t="n">
-        <v>-1.2454</v>
+        <v>0.09719999999999999</v>
       </c>
       <c r="V22" t="n">
-        <v>-0.2477</v>
+        <v>-1.5213</v>
       </c>
       <c r="W22" t="n">
-        <v>-0.0177</v>
+        <v>0.4599</v>
       </c>
       <c r="X22" t="n">
-        <v>-0.23</v>
+        <v>-1.9813</v>
       </c>
     </row>
     <row r="23">
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-7.9913</v>
+        <v>-7.8929</v>
       </c>
       <c r="E23" t="n">
-        <v>-7.1314</v>
+        <v>-7.2385</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.8599</v>
+        <v>-0.6544</v>
       </c>
       <c r="G23" t="n">
         <v>-5.0685</v>
@@ -2248,13 +2248,13 @@
         <v>1.8731</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.6335</v>
+        <v>-0.5352</v>
       </c>
       <c r="T23" t="n">
-        <v>0.6582</v>
+        <v>0.5511</v>
       </c>
       <c r="U23" t="n">
-        <v>-1.2917</v>
+        <v>-1.0862</v>
       </c>
       <c r="V23" t="n">
         <v>0</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-4.2263</v>
+        <v>-2.797499999999999</v>
       </c>
       <c r="E24" t="n">
-        <v>-0.2867000000000024</v>
+        <v>-0.2866000000000009</v>
       </c>
       <c r="F24" t="n">
-        <v>-3.9396</v>
+        <v>-2.5108</v>
       </c>
       <c r="G24" t="n">
         <v>5.307</v>
@@ -2326,13 +2326,13 @@
         <v>15.6089</v>
       </c>
       <c r="S24" t="n">
-        <v>-4.4886</v>
+        <v>-3.0597</v>
       </c>
       <c r="T24" t="n">
         <v>0.4789999999999998</v>
       </c>
       <c r="U24" t="n">
-        <v>-4.9676</v>
+        <v>-3.5389</v>
       </c>
       <c r="V24" t="n">
         <v>-6.0854</v>
